--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/145.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/145.xlsx
@@ -426,13 +426,13 @@
         <v>-7.187006391429557</v>
       </c>
       <c r="E2">
-        <v>-7.963581889544034</v>
+        <v>-9.355613729286816</v>
       </c>
       <c r="F2">
-        <v>-0.53639537668448</v>
+        <v>-0.9421115064928163</v>
       </c>
       <c r="G2">
-        <v>-6.676698092559601</v>
+        <v>-5.752424017201538</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.348100948212632</v>
       </c>
       <c r="E3">
-        <v>-8.073392796972501</v>
+        <v>-9.324817667313212</v>
       </c>
       <c r="F3">
-        <v>-0.4880866464880185</v>
+        <v>-0.7872962658488111</v>
       </c>
       <c r="G3">
-        <v>-6.594720712398644</v>
+        <v>-5.357705542471121</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.529631467545472</v>
       </c>
       <c r="E4">
-        <v>-9.888346145922572</v>
+        <v>-10.37346199471917</v>
       </c>
       <c r="F4">
-        <v>-0.5600866844045459</v>
+        <v>-0.9527311765967059</v>
       </c>
       <c r="G4">
-        <v>-6.884740496791646</v>
+        <v>-5.126054174901638</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.699002195658283</v>
       </c>
       <c r="E5">
-        <v>-10.58002611317084</v>
+        <v>-10.98409619617474</v>
       </c>
       <c r="F5">
-        <v>-0.3447509213120088</v>
+        <v>-1.019040330456001</v>
       </c>
       <c r="G5">
-        <v>-6.33475843048313</v>
+        <v>-5.18173091405172</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.85290142156374</v>
       </c>
       <c r="E6">
-        <v>-11.53551806377222</v>
+        <v>-11.98385722628746</v>
       </c>
       <c r="F6">
-        <v>0.449187047124941</v>
+        <v>-0.6630974844122756</v>
       </c>
       <c r="G6">
-        <v>-6.214776441309336</v>
+        <v>-4.744728819923631</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.977713458216342</v>
       </c>
       <c r="E7">
-        <v>-12.63156714523977</v>
+        <v>-12.37317094945424</v>
       </c>
       <c r="F7">
-        <v>-0.04842981908477805</v>
+        <v>-0.7690912354374864</v>
       </c>
       <c r="G7">
-        <v>-5.516600679775457</v>
+        <v>-4.699659536047244</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.06156633017944</v>
       </c>
       <c r="E8">
-        <v>-11.63254538674287</v>
+        <v>-12.74310578857937</v>
       </c>
       <c r="F8">
-        <v>-0.4759982809789653</v>
+        <v>-0.6911244671185941</v>
       </c>
       <c r="G8">
-        <v>-5.938348193257671</v>
+        <v>-4.839404861775764</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.094568291492852</v>
       </c>
       <c r="E9">
-        <v>-14.55591192727451</v>
+        <v>-13.56977758351854</v>
       </c>
       <c r="F9">
-        <v>-0.07557376213971224</v>
+        <v>-0.5391861464645116</v>
       </c>
       <c r="G9">
-        <v>-6.514620457598697</v>
+        <v>-4.575811034134011</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.064591426544519</v>
       </c>
       <c r="E10">
-        <v>-13.66749433956911</v>
+        <v>-14.20586681718398</v>
       </c>
       <c r="F10">
-        <v>0.2113304594524937</v>
+        <v>-0.4397812297611681</v>
       </c>
       <c r="G10">
-        <v>-6.058938485921193</v>
+        <v>-4.388440505574402</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.966942467497392</v>
       </c>
       <c r="E11">
-        <v>-14.27326928377462</v>
+        <v>-15.22019731262421</v>
       </c>
       <c r="F11">
-        <v>0.6518156542585336</v>
+        <v>-0.1505807737284019</v>
       </c>
       <c r="G11">
-        <v>-4.983340432573022</v>
+        <v>-4.064922257332825</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.799903797413841</v>
       </c>
       <c r="E12">
-        <v>-15.92371393214824</v>
+        <v>-16.20952132267764</v>
       </c>
       <c r="F12">
-        <v>0.9656086817456115</v>
+        <v>-0.3892789826820934</v>
       </c>
       <c r="G12">
-        <v>-5.818410586741926</v>
+        <v>-3.621320200878403</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.569234137155526</v>
       </c>
       <c r="E13">
-        <v>-15.22793889853369</v>
+        <v>-17.06569337765707</v>
       </c>
       <c r="F13">
-        <v>0.6679870426959856</v>
+        <v>0.07719126918236417</v>
       </c>
       <c r="G13">
-        <v>-5.105661648900453</v>
+        <v>-3.523975978054153</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.292608429496841</v>
       </c>
       <c r="E14">
-        <v>-15.8326090885268</v>
+        <v>-17.9428931415741</v>
       </c>
       <c r="F14">
-        <v>0.5033713873094594</v>
+        <v>0.2776785465797201</v>
       </c>
       <c r="G14">
-        <v>-4.321266047245057</v>
+        <v>-3.449765563051758</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.989151623644367</v>
       </c>
       <c r="E15">
-        <v>-18.3613831742978</v>
+        <v>-19.39895919352309</v>
       </c>
       <c r="F15">
-        <v>1.160009943834599</v>
+        <v>0.7633644370869178</v>
       </c>
       <c r="G15">
-        <v>-3.595763622075995</v>
+        <v>-3.240459558437614</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.686864762399296</v>
       </c>
       <c r="E16">
-        <v>-18.83619075258618</v>
+        <v>-19.4236832605398</v>
       </c>
       <c r="F16">
-        <v>1.502669090207032</v>
+        <v>1.040696873339775</v>
       </c>
       <c r="G16">
-        <v>-3.59019490386315</v>
+        <v>-3.032247455807147</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.407143210042846</v>
       </c>
       <c r="E17">
-        <v>-18.74378180060874</v>
+        <v>-20.18280307328063</v>
       </c>
       <c r="F17">
-        <v>0.9711951915100914</v>
+        <v>1.270101628401459</v>
       </c>
       <c r="G17">
-        <v>-2.607964909326963</v>
+        <v>-2.680475729600543</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.174277291686773</v>
       </c>
       <c r="E18">
-        <v>-19.88417471939149</v>
+        <v>-21.03429445909698</v>
       </c>
       <c r="F18">
-        <v>2.025592580572276</v>
+        <v>1.864183535401986</v>
       </c>
       <c r="G18">
-        <v>-3.031506004343271</v>
+        <v>-2.491512646840355</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.003697562985773</v>
       </c>
       <c r="E19">
-        <v>-20.99999308676522</v>
+        <v>-21.69302284769406</v>
       </c>
       <c r="F19">
-        <v>2.256712056157755</v>
+        <v>2.051830289688547</v>
       </c>
       <c r="G19">
-        <v>-2.136036274058961</v>
+        <v>-2.055434756297521</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.903773102372019</v>
       </c>
       <c r="E20">
-        <v>-22.65753142008164</v>
+        <v>-22.62458399464178</v>
       </c>
       <c r="F20">
-        <v>1.8884215656079</v>
+        <v>2.596886100321788</v>
       </c>
       <c r="G20">
-        <v>-2.895355673916713</v>
+        <v>-1.968013973664092</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.878870134171667</v>
       </c>
       <c r="E21">
-        <v>-22.11128030058357</v>
+        <v>-23.52832693213579</v>
       </c>
       <c r="F21">
-        <v>2.728316529184764</v>
+        <v>3.195318592921819</v>
       </c>
       <c r="G21">
-        <v>-1.644391295638872</v>
+        <v>-1.819316404732644</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.919916473288131</v>
       </c>
       <c r="E22">
-        <v>-23.22310327866282</v>
+        <v>-24.04202102805854</v>
       </c>
       <c r="F22">
-        <v>3.575844070011022</v>
+        <v>3.19482488594975</v>
       </c>
       <c r="G22">
-        <v>-2.228910902143225</v>
+        <v>-1.997536273500401</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.01753979079754</v>
       </c>
       <c r="E23">
-        <v>-25.01610690576117</v>
+        <v>-24.52555450334038</v>
       </c>
       <c r="F23">
-        <v>3.924646389042615</v>
+        <v>3.272376642199839</v>
       </c>
       <c r="G23">
-        <v>-2.581854852671239</v>
+        <v>-1.217868730299512</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.151246053170771</v>
       </c>
       <c r="E24">
-        <v>-23.37537246546501</v>
+        <v>-24.81073475895973</v>
       </c>
       <c r="F24">
-        <v>3.717355730166067</v>
+        <v>3.54566498879223</v>
       </c>
       <c r="G24">
-        <v>-2.168461721880588</v>
+        <v>-1.543010861676761</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.303352105057464</v>
       </c>
       <c r="E25">
-        <v>-26.125367352453</v>
+        <v>-24.88672191335879</v>
       </c>
       <c r="F25">
-        <v>3.803010576350341</v>
+        <v>3.533729871252695</v>
       </c>
       <c r="G25">
-        <v>-1.724426281824041</v>
+        <v>-1.615365037274874</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.452646868953856</v>
       </c>
       <c r="E26">
-        <v>-25.10344063349967</v>
+        <v>-25.56293116842208</v>
       </c>
       <c r="F26">
-        <v>3.277515833566808</v>
+        <v>3.680312796647679</v>
       </c>
       <c r="G26">
-        <v>-1.908311466354514</v>
+        <v>-2.074754266271759</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.579313360996809</v>
       </c>
       <c r="E27">
-        <v>-26.15930324218818</v>
+        <v>-25.8582950982099</v>
       </c>
       <c r="F27">
-        <v>3.379086931028472</v>
+        <v>3.838017382792648</v>
       </c>
       <c r="G27">
-        <v>-2.407370959413365</v>
+        <v>-1.953365085763356</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.669637600958873</v>
       </c>
       <c r="E28">
-        <v>-25.10631050252513</v>
+        <v>-26.07632623312943</v>
       </c>
       <c r="F28">
-        <v>3.42467530267414</v>
+        <v>3.463507509782575</v>
       </c>
       <c r="G28">
-        <v>-2.885878671050973</v>
+        <v>-2.187541043352444</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.708383457316174</v>
       </c>
       <c r="E29">
-        <v>-26.52578260949105</v>
+        <v>-25.9444908460454</v>
       </c>
       <c r="F29">
-        <v>4.071207776885126</v>
+        <v>3.208676845659363</v>
       </c>
       <c r="G29">
-        <v>-3.72208188837242</v>
+        <v>-2.111174153317789</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.6895452159279</v>
       </c>
       <c r="E30">
-        <v>-26.0763220799181</v>
+        <v>-25.48395370186913</v>
       </c>
       <c r="F30">
-        <v>3.45908237111682</v>
+        <v>3.247076644983537</v>
       </c>
       <c r="G30">
-        <v>-2.424236369471957</v>
+        <v>-2.125191241027477</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.60682643704986</v>
       </c>
       <c r="E31">
-        <v>-25.24778133988276</v>
+        <v>-25.86071642041228</v>
       </c>
       <c r="F31">
-        <v>3.155797184134254</v>
+        <v>3.208767966073671</v>
       </c>
       <c r="G31">
-        <v>-2.801105183432933</v>
+        <v>-2.043741231273924</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.460379511662601</v>
       </c>
       <c r="E32">
-        <v>-25.20114077670494</v>
+        <v>-24.90801958103251</v>
       </c>
       <c r="F32">
-        <v>3.141267619889151</v>
+        <v>3.180851984599328</v>
       </c>
       <c r="G32">
-        <v>-3.419527919197483</v>
+        <v>-1.867385434144222</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.254192950299593</v>
       </c>
       <c r="E33">
-        <v>-24.73777114240514</v>
+        <v>-24.7618680745118</v>
       </c>
       <c r="F33">
-        <v>2.88892868491356</v>
+        <v>2.883956823761957</v>
       </c>
       <c r="G33">
-        <v>-3.003557983495404</v>
+        <v>-1.821561645081001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.993095928774586</v>
       </c>
       <c r="E34">
-        <v>-23.05611511092544</v>
+        <v>-25.08056889873384</v>
       </c>
       <c r="F34">
-        <v>3.210891900094449</v>
+        <v>2.838235913331841</v>
       </c>
       <c r="G34">
-        <v>-2.412153843504285</v>
+        <v>-1.916211579487223</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.689926173667968</v>
       </c>
       <c r="E35">
-        <v>-23.41695857046052</v>
+        <v>-24.64041986895116</v>
       </c>
       <c r="F35">
-        <v>2.482452113829453</v>
+        <v>2.433628139108451</v>
       </c>
       <c r="G35">
-        <v>-1.804910316078881</v>
+        <v>-1.907222785860019</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.353109100687929</v>
       </c>
       <c r="E36">
-        <v>-23.15479541200337</v>
+        <v>-23.85434156150086</v>
       </c>
       <c r="F36">
-        <v>2.684287144991164</v>
+        <v>2.609425926065367</v>
       </c>
       <c r="G36">
-        <v>-1.908710910276954</v>
+        <v>-1.229865101695677</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.997051449953868</v>
       </c>
       <c r="E37">
-        <v>-22.33308255138604</v>
+        <v>-23.47318889858737</v>
       </c>
       <c r="F37">
-        <v>3.034790930668108</v>
+        <v>2.494697040777636</v>
       </c>
       <c r="G37">
-        <v>-2.042540288762012</v>
+        <v>-0.9006893699251589</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.633114760593759</v>
       </c>
       <c r="E38">
-        <v>-20.9683414632587</v>
+        <v>-23.22404190442223</v>
       </c>
       <c r="F38">
-        <v>2.661977554098968</v>
+        <v>2.300885576279441</v>
       </c>
       <c r="G38">
-        <v>-2.568602713126748</v>
+        <v>-0.5350389254721966</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.272533147487731</v>
       </c>
       <c r="E39">
-        <v>-22.22526933860481</v>
+        <v>-22.75965888655918</v>
       </c>
       <c r="F39">
-        <v>2.820770615011216</v>
+        <v>2.307012181590546</v>
       </c>
       <c r="G39">
-        <v>-1.367242482080059</v>
+        <v>-1.01700848443762</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.928371907033303</v>
       </c>
       <c r="E40">
-        <v>-21.54737803295497</v>
+        <v>-22.20607319586146</v>
       </c>
       <c r="F40">
-        <v>2.371344850826761</v>
+        <v>2.210750919180827</v>
       </c>
       <c r="G40">
-        <v>-1.31663841967051</v>
+        <v>-0.2433743719867936</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.607840054771932</v>
       </c>
       <c r="E41">
-        <v>-21.40979460139738</v>
+        <v>-22.17843357449472</v>
       </c>
       <c r="F41">
-        <v>2.410637630211153</v>
+        <v>2.240123170549292</v>
       </c>
       <c r="G41">
-        <v>-0.6426538175178862</v>
+        <v>-0.1936214123139477</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.323797942167597</v>
       </c>
       <c r="E42">
-        <v>-21.36282178131357</v>
+        <v>-21.15742056203285</v>
       </c>
       <c r="F42">
-        <v>2.498055242228585</v>
+        <v>2.057592413342421</v>
       </c>
       <c r="G42">
-        <v>-1.366728165395609</v>
+        <v>0.1281267510948536</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.081374429251168</v>
       </c>
       <c r="E43">
-        <v>-20.1770259563278</v>
+        <v>-20.52585832871147</v>
       </c>
       <c r="F43">
-        <v>2.338117377565668</v>
+        <v>2.034174466865279</v>
       </c>
       <c r="G43">
-        <v>-1.266671378941193</v>
+        <v>0.4996435386440475</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.888600366719723</v>
       </c>
       <c r="E44">
-        <v>-18.94036990545818</v>
+        <v>-20.46712361415575</v>
       </c>
       <c r="F44">
-        <v>2.598276100823686</v>
+        <v>1.669626540241272</v>
       </c>
       <c r="G44">
-        <v>-1.758266753214051</v>
+        <v>0.4511933405221672</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.747043104252435</v>
       </c>
       <c r="E45">
-        <v>-19.00421306994344</v>
+        <v>-19.88373447899106</v>
       </c>
       <c r="F45">
-        <v>2.397599127291089</v>
+        <v>1.918759693368029</v>
       </c>
       <c r="G45">
-        <v>-0.1444689238970578</v>
+        <v>0.8880309577410155</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.655797552621541</v>
       </c>
       <c r="E46">
-        <v>-18.76802824832309</v>
+        <v>-19.7039378075279</v>
       </c>
       <c r="F46">
-        <v>2.447774997613461</v>
+        <v>1.638542881818624</v>
       </c>
       <c r="G46">
-        <v>-0.8161769567662307</v>
+        <v>0.7319841427855833</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.613247797938927</v>
       </c>
       <c r="E47">
-        <v>-18.63668294017539</v>
+        <v>-18.80112518937065</v>
       </c>
       <c r="F47">
-        <v>2.025802985892587</v>
+        <v>1.925903533849772</v>
       </c>
       <c r="G47">
-        <v>-0.2907358896141797</v>
+        <v>1.019667310769538</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.614019315601404</v>
       </c>
       <c r="E48">
-        <v>-17.28214629227316</v>
+        <v>-19.0898522874614</v>
       </c>
       <c r="F48">
-        <v>2.304094671597886</v>
+        <v>1.676417496209422</v>
       </c>
       <c r="G48">
-        <v>-1.296929908752195</v>
+        <v>1.059690025351305</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.655230347158533</v>
       </c>
       <c r="E49">
-        <v>-17.52299932342261</v>
+        <v>-17.46747504122098</v>
       </c>
       <c r="F49">
-        <v>1.664768993791256</v>
+        <v>1.89084205515888</v>
       </c>
       <c r="G49">
-        <v>-0.5669526673539653</v>
+        <v>0.9978597611999692</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.729937810467444</v>
       </c>
       <c r="E50">
-        <v>-16.87604528893142</v>
+        <v>-17.30265900300649</v>
       </c>
       <c r="F50">
-        <v>1.979853446059298</v>
+        <v>1.386324888483841</v>
       </c>
       <c r="G50">
-        <v>-0.3569939765920438</v>
+        <v>1.080983258236425</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.834876976590674</v>
       </c>
       <c r="E51">
-        <v>-16.41399637583292</v>
+        <v>-17.313316143266</v>
       </c>
       <c r="F51">
-        <v>2.499665588459627</v>
+        <v>1.660652007799342</v>
       </c>
       <c r="G51">
-        <v>-0.4247114697963402</v>
+        <v>1.587752280072834</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.96332513593226</v>
       </c>
       <c r="E52">
-        <v>-15.39668387466147</v>
+        <v>-17.20562337361319</v>
       </c>
       <c r="F52">
-        <v>2.126530805338201</v>
+        <v>1.482118951678382</v>
       </c>
       <c r="G52">
-        <v>-1.369365017432634</v>
+        <v>0.8715989312845485</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.110700682198767</v>
       </c>
       <c r="E53">
-        <v>-14.9496778929815</v>
+        <v>-16.40397052369479</v>
       </c>
       <c r="F53">
-        <v>1.731631497075621</v>
+        <v>1.170927826203497</v>
       </c>
       <c r="G53">
-        <v>-1.028070209270167</v>
+        <v>0.912193398931769</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.269802391628169</v>
       </c>
       <c r="E54">
-        <v>-13.81660708576443</v>
+        <v>-16.54521708764088</v>
       </c>
       <c r="F54">
-        <v>1.780341157095037</v>
+        <v>1.395630767886891</v>
       </c>
       <c r="G54">
-        <v>-0.3182896880287893</v>
+        <v>0.8280412685264145</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.434228935735335</v>
       </c>
       <c r="E55">
-        <v>-15.53333283367098</v>
+        <v>-16.07224107554676</v>
       </c>
       <c r="F55">
-        <v>1.940607055249463</v>
+        <v>1.108447386479942</v>
       </c>
       <c r="G55">
-        <v>-1.675487874463622</v>
+        <v>0.8157133325671775</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.597903503032991</v>
       </c>
       <c r="E56">
-        <v>-14.92970094650907</v>
+        <v>-15.65992271485175</v>
       </c>
       <c r="F56">
-        <v>1.765947445103993</v>
+        <v>1.24714591093508</v>
       </c>
       <c r="G56">
-        <v>-1.251925893490585</v>
+        <v>0.4523603433543948</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.752857168258982</v>
       </c>
       <c r="E57">
-        <v>-14.36297034196827</v>
+        <v>-15.23626193402864</v>
       </c>
       <c r="F57">
-        <v>1.616458606859989</v>
+        <v>1.309245301653347</v>
       </c>
       <c r="G57">
-        <v>-1.564627826891179</v>
+        <v>0.1303876559107577</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.894488594360985</v>
       </c>
       <c r="E58">
-        <v>-14.3476865242929</v>
+        <v>-15.35456200540506</v>
       </c>
       <c r="F58">
-        <v>1.5959266924142</v>
+        <v>1.140558220482061</v>
       </c>
       <c r="G58">
-        <v>-1.864654595301917</v>
+        <v>-0.2418366434226278</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.015565853717932</v>
       </c>
       <c r="E59">
-        <v>-14.48255375564406</v>
+        <v>-14.47903598565193</v>
       </c>
       <c r="F59">
-        <v>1.772062453271459</v>
+        <v>1.026364460536539</v>
       </c>
       <c r="G59">
-        <v>-1.162142387002199</v>
+        <v>-0.3733424592215951</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.112758120781298</v>
       </c>
       <c r="E60">
-        <v>-13.56302446190437</v>
+        <v>-14.67473115006653</v>
       </c>
       <c r="F60">
-        <v>1.169516288149127</v>
+        <v>1.343940641952202</v>
       </c>
       <c r="G60">
-        <v>-2.544696124905924</v>
+        <v>-0.3628603196882753</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.183371712333352</v>
       </c>
       <c r="E61">
-        <v>-14.36751395515763</v>
+        <v>-14.45250942492025</v>
       </c>
       <c r="F61">
-        <v>1.562387753009654</v>
+        <v>1.213442954784779</v>
       </c>
       <c r="G61">
-        <v>-2.485505323536203</v>
+        <v>-0.7798197275903871</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.226845258452575</v>
       </c>
       <c r="E62">
-        <v>-13.14992114426897</v>
+        <v>-14.44293211960519</v>
       </c>
       <c r="F62">
-        <v>1.710715220154933</v>
+        <v>1.266369004884445</v>
       </c>
       <c r="G62">
-        <v>-3.300070689686504</v>
+        <v>-1.182876920544821</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.244897166899944</v>
       </c>
       <c r="E63">
-        <v>-11.49280643850769</v>
+        <v>-13.91782499896182</v>
       </c>
       <c r="F63">
-        <v>1.595770959342474</v>
+        <v>1.342462834505608</v>
       </c>
       <c r="G63">
-        <v>-3.03591033046848</v>
+        <v>-1.838333068334313</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.237087422764911</v>
       </c>
       <c r="E64">
-        <v>-12.82084144494618</v>
+        <v>-13.38895506885816</v>
       </c>
       <c r="F64">
-        <v>2.003125599873548</v>
+        <v>1.13086135166489</v>
       </c>
       <c r="G64">
-        <v>-3.50994583662151</v>
+        <v>-1.736623680553722</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.206013506340267</v>
       </c>
       <c r="E65">
-        <v>-12.77720780676754</v>
+        <v>-13.89580051930626</v>
       </c>
       <c r="F65">
-        <v>1.575613466962751</v>
+        <v>1.140089364532077</v>
       </c>
       <c r="G65">
-        <v>-3.718612208810831</v>
+        <v>-1.806346225603993</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.152444950578442</v>
       </c>
       <c r="E66">
-        <v>-14.02673050632148</v>
+        <v>-13.67811825413802</v>
       </c>
       <c r="F66">
-        <v>1.01408805562705</v>
+        <v>0.9693860371023773</v>
       </c>
       <c r="G66">
-        <v>-2.926462695719828</v>
+        <v>-2.636166172400169</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.076367013690421</v>
       </c>
       <c r="E67">
-        <v>-12.70582241051638</v>
+        <v>-12.57858878158026</v>
       </c>
       <c r="F67">
-        <v>1.368105775826669</v>
+        <v>0.725501419839758</v>
       </c>
       <c r="G67">
-        <v>-3.798098938631866</v>
+        <v>-2.581677322039043</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.979728181401747</v>
       </c>
       <c r="E68">
-        <v>-12.21082607197802</v>
+        <v>-13.32926926890904</v>
       </c>
       <c r="F68">
-        <v>1.464310709252998</v>
+        <v>1.073886241700341</v>
       </c>
       <c r="G68">
-        <v>-4.27849944009803</v>
+        <v>-3.225285910874064</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.860217500566495</v>
       </c>
       <c r="E69">
-        <v>-11.83757697021568</v>
+        <v>-13.4448157611771</v>
       </c>
       <c r="F69">
-        <v>1.256880884652779</v>
+        <v>0.9083287325768313</v>
       </c>
       <c r="G69">
-        <v>-4.518920298749062</v>
+        <v>-3.239958295476121</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.718511759625795</v>
       </c>
       <c r="E70">
-        <v>-11.98916503036059</v>
+        <v>-12.7291094664147</v>
       </c>
       <c r="F70">
-        <v>0.8534079737712241</v>
+        <v>0.7006677934712316</v>
       </c>
       <c r="G70">
-        <v>-4.741637698327754</v>
+        <v>-2.998832535785489</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.552148753344559</v>
       </c>
       <c r="E71">
-        <v>-11.07035839539143</v>
+        <v>-13.15207666094656</v>
       </c>
       <c r="F71">
-        <v>1.642721166998344</v>
+        <v>0.7800195920876047</v>
       </c>
       <c r="G71">
-        <v>-4.276961711533865</v>
+        <v>-3.336075468342548</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.360592021828761</v>
       </c>
       <c r="E72">
-        <v>-11.02840265458801</v>
+        <v>-12.94421674056154</v>
       </c>
       <c r="F72">
-        <v>1.507064407646286</v>
+        <v>0.9916641500332672</v>
       </c>
       <c r="G72">
-        <v>-4.380054793947746</v>
+        <v>-2.885549717232492</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.146758922566383</v>
       </c>
       <c r="E73">
-        <v>-13.01559798360137</v>
+        <v>-12.61590538533384</v>
       </c>
       <c r="F73">
-        <v>0.741830198083742</v>
+        <v>0.5892747437145738</v>
       </c>
       <c r="G73">
-        <v>-4.280170316636343</v>
+        <v>-3.349291057462763</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.912040006441825</v>
       </c>
       <c r="E74">
-        <v>-12.40418713162806</v>
+        <v>-12.84888808102275</v>
       </c>
       <c r="F74">
-        <v>0.9535161743995444</v>
+        <v>0.7409720094544416</v>
       </c>
       <c r="G74">
-        <v>-4.875558452873501</v>
+        <v>-3.472058711115274</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.664869880838696</v>
       </c>
       <c r="E75">
-        <v>-12.63491048035626</v>
+        <v>-13.17667613162352</v>
       </c>
       <c r="F75">
-        <v>0.4174009331447183</v>
+        <v>0.6588799714696079</v>
       </c>
       <c r="G75">
-        <v>-4.093807535488903</v>
+        <v>-3.675284291576714</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.408740088420957</v>
       </c>
       <c r="E76">
-        <v>-12.72279243198963</v>
+        <v>-13.4241743008927</v>
       </c>
       <c r="F76">
-        <v>0.7921965929087574</v>
+        <v>0.9176230148362418</v>
       </c>
       <c r="G76">
-        <v>-5.035732855027483</v>
+        <v>-3.574298080047861</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.151532173350653</v>
       </c>
       <c r="E77">
-        <v>-13.95237141076175</v>
+        <v>-13.73118383523535</v>
       </c>
       <c r="F77">
-        <v>0.5339108083484688</v>
+        <v>0.6005687048843422</v>
       </c>
       <c r="G77">
-        <v>-4.091118468560056</v>
+        <v>-3.071236315530833</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.898352728443571</v>
       </c>
       <c r="E78">
-        <v>-13.29377177171574</v>
+        <v>-14.70963473804038</v>
       </c>
       <c r="F78">
-        <v>0.3053145398719173</v>
+        <v>0.5264836662149684</v>
       </c>
       <c r="G78">
-        <v>-3.549125280700347</v>
+        <v>-2.922013986936571</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.652845916189269</v>
       </c>
       <c r="E79">
-        <v>-13.78539985586966</v>
+        <v>-14.82641058086059</v>
       </c>
       <c r="F79">
-        <v>0.6965955393190693</v>
+        <v>0.3630525762144456</v>
       </c>
       <c r="G79">
-        <v>-4.102647516674413</v>
+        <v>-2.95997682403595</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.420253728298997</v>
       </c>
       <c r="E80">
-        <v>-14.43591319246623</v>
+        <v>-14.44196026815519</v>
       </c>
       <c r="F80">
-        <v>0.03289432231766062</v>
+        <v>0.4013960465552291</v>
       </c>
       <c r="G80">
-        <v>-3.5195847056519</v>
+        <v>-3.23590119838153</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.199870083848619</v>
       </c>
       <c r="E81">
-        <v>-13.81147371656694</v>
+        <v>-15.27590018291281</v>
       </c>
       <c r="F81">
-        <v>1.135851436899355</v>
+        <v>0.3786192564478539</v>
       </c>
       <c r="G81">
-        <v>-3.001769623450491</v>
+        <v>-2.361988386186043</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.9957188409771818</v>
       </c>
       <c r="E82">
-        <v>-15.25274187656556</v>
+        <v>-15.62987423091662</v>
       </c>
       <c r="F82">
-        <v>0.1462423191449254</v>
+        <v>0.1884907134225058</v>
       </c>
       <c r="G82">
-        <v>-2.385994182701329</v>
+        <v>-2.762325183276536</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.8062621663834044</v>
       </c>
       <c r="E83">
-        <v>-15.91285743774514</v>
+        <v>-16.38717078388585</v>
       </c>
       <c r="F83">
-        <v>-0.2915523383368218</v>
+        <v>0.187134675984123</v>
       </c>
       <c r="G83">
-        <v>-4.203730325753137</v>
+        <v>-2.504323570548948</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.6327200243097669</v>
       </c>
       <c r="E84">
-        <v>-16.97063467685439</v>
+        <v>-17.66584487372877</v>
       </c>
       <c r="F84">
-        <v>0.2358319104924975</v>
+        <v>0.2822287687232978</v>
       </c>
       <c r="G84">
-        <v>-2.573777208906335</v>
+        <v>-2.51743734063011</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4754311016890095</v>
       </c>
       <c r="E85">
-        <v>-17.8430624009592</v>
+        <v>-18.64869402732679</v>
       </c>
       <c r="F85">
-        <v>0.08888118997067081</v>
+        <v>0.1641557642304647</v>
       </c>
       <c r="G85">
-        <v>-3.726039777172548</v>
+        <v>-2.55521742560811</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3351924592583168</v>
       </c>
       <c r="E86">
-        <v>-18.45729328342207</v>
+        <v>-18.86633891359311</v>
       </c>
       <c r="F86">
-        <v>0.1166372965362738</v>
+        <v>0.2604393925600596</v>
       </c>
       <c r="G86">
-        <v>-3.582031105526739</v>
+        <v>-2.514186963614174</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2157511095708213</v>
       </c>
       <c r="E87">
-        <v>-20.02582414483609</v>
+        <v>-20.19723548263441</v>
       </c>
       <c r="F87">
-        <v>-0.3318325316653505</v>
+        <v>0.009347978893084669</v>
       </c>
       <c r="G87">
-        <v>-3.943548741291969</v>
+        <v>-2.571599847917346</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.1198695560624551</v>
       </c>
       <c r="E88">
-        <v>-20.55099771686066</v>
+        <v>-21.6594898194574</v>
       </c>
       <c r="F88">
-        <v>-0.09868935451483245</v>
+        <v>-0.03044182093298678</v>
       </c>
       <c r="G88">
-        <v>-3.386551604267132</v>
+        <v>-2.774710555616778</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.05308459436107417</v>
       </c>
       <c r="E89">
-        <v>-20.80257433965082</v>
+        <v>-22.27358779915787</v>
       </c>
       <c r="F89">
-        <v>-0.3683941837227123</v>
+        <v>0.1117954890669107</v>
       </c>
       <c r="G89">
-        <v>-3.734587354963853</v>
+        <v>-2.646710969803675</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.01915246607566222</v>
       </c>
       <c r="E90">
-        <v>-22.34887306084304</v>
+        <v>-23.02688065640997</v>
       </c>
       <c r="F90">
-        <v>-0.2719863002826974</v>
+        <v>-0.212641231178738</v>
       </c>
       <c r="G90">
-        <v>-2.980327578123678</v>
+        <v>-2.379245407933301</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.02328079213876418</v>
       </c>
       <c r="E91">
-        <v>-25.81835781811035</v>
+        <v>-25.6107429371935</v>
       </c>
       <c r="F91">
-        <v>-0.0006901772940397403</v>
+        <v>-0.3579029105662566</v>
       </c>
       <c r="G91">
-        <v>-3.073512884814284</v>
+        <v>-2.997044175740576</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.06833285088154575</v>
       </c>
       <c r="E92">
-        <v>-26.88866114257529</v>
+        <v>-26.78461904567702</v>
       </c>
       <c r="F92">
-        <v>-0.134875756138726</v>
+        <v>-0.1791354264703036</v>
       </c>
       <c r="G92">
-        <v>-4.254023709556344</v>
+        <v>-3.112645335490481</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.1590571891394892</v>
       </c>
       <c r="E93">
-        <v>-28.8240410071001</v>
+        <v>-28.85316540151545</v>
       </c>
       <c r="F93">
-        <v>0.04295401605725781</v>
+        <v>-0.1048076761519096</v>
       </c>
       <c r="G93">
-        <v>-3.005983365220548</v>
+        <v>-2.933389001120052</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2963743512669977</v>
       </c>
       <c r="E94">
-        <v>-31.16406202118595</v>
+        <v>-30.15846365255618</v>
       </c>
       <c r="F94">
-        <v>-0.02357382679637608</v>
+        <v>-0.1653033475783575</v>
       </c>
       <c r="G94">
-        <v>-3.154242329060689</v>
+        <v>-3.082512121419852</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4818725302840396</v>
       </c>
       <c r="E95">
-        <v>-33.07887725983586</v>
+        <v>-32.9447617597345</v>
       </c>
       <c r="F95">
-        <v>-0.8381986143834379</v>
+        <v>-0.4126919589548186</v>
       </c>
       <c r="G95">
-        <v>-4.402217404781706</v>
+        <v>-2.966843082310578</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.7179704389490353</v>
       </c>
       <c r="E96">
-        <v>-34.88394596583284</v>
+        <v>-34.74895829135327</v>
       </c>
       <c r="F96">
-        <v>-0.6699986132449983</v>
+        <v>-0.3421200264407176</v>
       </c>
       <c r="G96">
-        <v>-3.790472953681224</v>
+        <v>-3.309101255227165</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.9971309174353997</v>
       </c>
       <c r="E97">
-        <v>-36.09322820086052</v>
+        <v>-36.54356921123433</v>
       </c>
       <c r="F97">
-        <v>-0.1100031965022681</v>
+        <v>-0.6963879135959822</v>
       </c>
       <c r="G97">
-        <v>-4.081077544862635</v>
+        <v>-3.701363019297345</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.32618891110313</v>
       </c>
       <c r="E98">
-        <v>-39.30302719022595</v>
+        <v>-38.63559574729769</v>
       </c>
       <c r="F98">
-        <v>-0.1306088356469058</v>
+        <v>-0.5564484947714504</v>
       </c>
       <c r="G98">
-        <v>-4.158734142725299</v>
+        <v>-3.199841594089074</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.682061740725539</v>
       </c>
       <c r="E99">
-        <v>-40.9183585134538</v>
+        <v>-40.66208876186658</v>
       </c>
       <c r="F99">
-        <v>-0.6326102505196426</v>
+        <v>-0.261696320405122</v>
       </c>
       <c r="G99">
-        <v>-3.965878439779761</v>
+        <v>-3.943556573525743</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.081956953225359</v>
       </c>
       <c r="E100">
-        <v>-44.43057150883096</v>
+        <v>-43.07574205953033</v>
       </c>
       <c r="F100">
-        <v>-0.3624697000578902</v>
+        <v>-0.6761127930450614</v>
       </c>
       <c r="G100">
-        <v>-5.383379604780128</v>
+        <v>-4.034091974456369</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.474202531226418</v>
       </c>
       <c r="E101">
-        <v>-44.73403835391353</v>
+        <v>-44.91721781600075</v>
       </c>
       <c r="F101">
-        <v>-0.4720461401002088</v>
+        <v>-0.5593452955790403</v>
       </c>
       <c r="G101">
-        <v>-4.72802788677428</v>
+        <v>-4.358688460214075</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.911662085701848</v>
       </c>
       <c r="E102">
-        <v>-47.71659023242964</v>
+        <v>-47.06608831716421</v>
       </c>
       <c r="F102">
-        <v>-0.7738957663737235</v>
+        <v>-0.5827491598103347</v>
       </c>
       <c r="G102">
-        <v>-6.317718100536934</v>
+        <v>-3.94763194583247</v>
       </c>
     </row>
   </sheetData>
